--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N128_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N128_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.98388120742266</v>
+        <v>9.909880696206182</v>
       </c>
       <c r="D2" t="n">
-        <v>53.24257169294012</v>
+        <v>8.65191790010277</v>
       </c>
       <c r="E2" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F2" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.59058110834135</v>
+        <v>8.708469430105469</v>
       </c>
       <c r="D3" t="n">
-        <v>51.17505258960414</v>
+        <v>8.315946045810673</v>
       </c>
       <c r="E3" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F3" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.7116259553306</v>
+        <v>8.728139217741223</v>
       </c>
       <c r="D4" t="n">
-        <v>34.46279823091349</v>
+        <v>5.600204712523442</v>
       </c>
       <c r="E4" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F4" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.00537969231682</v>
+        <v>6.663374200001484</v>
       </c>
       <c r="D5" t="n">
-        <v>40.17516373720697</v>
+        <v>6.528464107296133</v>
       </c>
       <c r="E5" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F5" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.65497570679601</v>
+        <v>5.306433552354352</v>
       </c>
       <c r="D6" t="n">
-        <v>9.429715092301928</v>
+        <v>1.532328702499063</v>
       </c>
       <c r="E6" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F6" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.80955876702669</v>
+        <v>2.081553299641837</v>
       </c>
       <c r="D7" t="n">
-        <v>24.08991012385229</v>
+        <v>3.914610395125997</v>
       </c>
       <c r="E7" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F7" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.77227654935618</v>
+        <v>7.600494939270379</v>
       </c>
       <c r="D8" t="n">
-        <v>22.52747604549496</v>
+        <v>3.660714857392931</v>
       </c>
       <c r="E8" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F8" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.19489854155103</v>
+        <v>2.794171013002043</v>
       </c>
       <c r="D9" t="n">
-        <v>16.58195631323786</v>
+        <v>2.694567900901153</v>
       </c>
       <c r="E9" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F9" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.78672307291245</v>
+        <v>2.402842499348273</v>
       </c>
       <c r="D10" t="n">
-        <v>14.02243615315753</v>
+        <v>2.278645874888099</v>
       </c>
       <c r="E10" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F10" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>57.76961322302375</v>
+        <v>9.38756214874136</v>
       </c>
       <c r="D11" t="n">
-        <v>44.95351178965021</v>
+        <v>7.30494566581816</v>
       </c>
       <c r="E11" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F11" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>56.58666411699209</v>
+        <v>9.195332919011214</v>
       </c>
       <c r="D12" t="n">
-        <v>28.84174435497508</v>
+        <v>4.686783457683451</v>
       </c>
       <c r="E12" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F12" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.08022985290955</v>
+        <v>3.588037351097803</v>
       </c>
       <c r="D13" t="n">
-        <v>22.99041410978246</v>
+        <v>3.73594229283965</v>
       </c>
       <c r="E13" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F13" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24.92079880563554</v>
+        <v>4.049629805915775</v>
       </c>
       <c r="D14" t="n">
-        <v>25.44788719976632</v>
+        <v>4.135281669962027</v>
       </c>
       <c r="E14" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F14" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>34.73786551933122</v>
+        <v>5.644903146891324</v>
       </c>
       <c r="D15" t="n">
-        <v>34.43720114378964</v>
+        <v>5.596045185865816</v>
       </c>
       <c r="E15" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F15" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>44.45442707774003</v>
+        <v>7.223844400132755</v>
       </c>
       <c r="D16" t="n">
-        <v>44.15481862737613</v>
+        <v>7.175158026948622</v>
       </c>
       <c r="E16" t="n">
-        <v>16.22962358252706</v>
+        <v>2.637313832160648</v>
       </c>
       <c r="F16" t="n">
-        <v>13.05861702871066</v>
+        <v>2.122025267165482</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
